--- a/Docs/Characters.xlsx
+++ b/Docs/Characters.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="3"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Toddy" sheetId="1" r:id="rId1"/>
-    <sheet name="Fabulous Jar" sheetId="2" r:id="rId2"/>
+    <sheet name="Fabulous Flask" sheetId="2" r:id="rId2"/>
     <sheet name="Topol" sheetId="3" r:id="rId3"/>
     <sheet name="Boss 1" sheetId="4" r:id="rId4"/>
   </sheets>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="114">
   <si>
     <t>Toddy/Knight/Boris</t>
   </si>
@@ -149,9 +149,6 @@
     <t>15th centruy knight, reference to Boris Todbringer</t>
   </si>
   <si>
-    <t>The fabulous jar</t>
-  </si>
-  <si>
     <t>The smug jug with Zaharov's face and headphones</t>
   </si>
   <si>
@@ -284,9 +281,6 @@
     <t>Weirdest units, often rely on combinations with each other and spawn next to each other</t>
   </si>
   <si>
-    <t>[Galapo, Armo, Hazar, Boxor, Watt]</t>
-  </si>
-  <si>
     <t>[Flesh construct, Luxurious eternal]</t>
   </si>
   <si>
@@ -299,15 +293,9 @@
     <t>Squad of infantrymen, Bomb mage, Storm mage</t>
   </si>
   <si>
-    <t>Spark of Raiju, Amphibia</t>
-  </si>
-  <si>
     <t>Battering boar, Roach mage, Water mage, Poison charge</t>
   </si>
   <si>
-    <t>[Skelic, Draculard], [Living olive, Crude mage], Water mage, Suspiciously tall goblin</t>
-  </si>
-  <si>
     <t>Nurgle/Great unclean made out of (recording equipment? Trees? Sickness?)</t>
   </si>
   <si>
@@ -366,6 +354,24 @@
   </si>
   <si>
     <t>Bigger map. All units deployed on the board gain "Undead"</t>
+  </si>
+  <si>
+    <t>Torch-bearer, Starving soldier, Goblin, Abandoned soldier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skelic, </t>
+  </si>
+  <si>
+    <t>The Fabulous Flask</t>
+  </si>
+  <si>
+    <t>[Skelic, Draculard], [Living olive, Crude mage], [Water mage, spark of Raiju]</t>
+  </si>
+  <si>
+    <t>[Spark of Raiju, Virus rat]</t>
+  </si>
+  <si>
+    <t>[Galapo, Armo, Hazar, Boxor, Watt], [Tallyman, Forest mage/Plague mage]</t>
   </si>
 </sst>
 </file>
@@ -952,7 +958,7 @@
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
@@ -960,51 +966,54 @@
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C21" s="9" t="s">
         <v>78</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>79</v>
       </c>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="B11:B15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="E5:E7"/>
@@ -1019,14 +1028,11 @@
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="B11:B15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1047,7 +1053,7 @@
   <sheetData>
     <row r="1" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B1" s="9" t="s">
-        <v>39</v>
+        <v>110</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -1055,7 +1061,7 @@
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
@@ -1078,11 +1084,11 @@
         <v>5</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
@@ -1090,11 +1096,11 @@
         <v>4</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
@@ -1114,7 +1120,7 @@
         <v>12</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
@@ -1122,7 +1128,7 @@
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" s="9"/>
       <c r="C9" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
@@ -1130,7 +1136,7 @@
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" s="9"/>
       <c r="C10" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
@@ -1140,50 +1146,50 @@
         <v>17</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E11" s="9"/>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" s="9"/>
       <c r="C12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>49</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>50</v>
       </c>
       <c r="E12" s="9"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" s="9"/>
       <c r="C13" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E13" s="9"/>
     </row>
     <row r="14" spans="2:5" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="9"/>
       <c r="C14" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E14" s="10"/>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" s="9"/>
       <c r="C15" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E15" s="9"/>
     </row>
@@ -1192,7 +1198,7 @@
         <v>31</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
@@ -1202,7 +1208,7 @@
         <v>34</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
@@ -1221,7 +1227,7 @@
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
@@ -1229,30 +1235,30 @@
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
     </row>
     <row r="23" spans="2:5" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
@@ -1260,29 +1266,30 @@
     <row r="24" spans="2:5" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="9"/>
       <c r="C24" s="9" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="C5:D7"/>
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="D12:E12"/>
@@ -1297,13 +1304,12 @@
     <mergeCell ref="C17:E18"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="C9:E9"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="C5:D7"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C24:E24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1323,7 +1329,7 @@
   <sheetData>
     <row r="1" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B1" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -1331,7 +1337,7 @@
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
@@ -1354,11 +1360,11 @@
         <v>5</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
@@ -1366,7 +1372,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10"/>
@@ -1388,17 +1394,17 @@
         <v>12</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" s="9"/>
       <c r="C9" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="10"/>
@@ -1406,7 +1412,7 @@
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" s="9"/>
       <c r="C10" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="10"/>
@@ -1416,13 +1422,13 @@
         <v>17</v>
       </c>
       <c r="C11" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" s="10" t="s">
         <v>68</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="12" spans="2:5" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1460,11 +1466,11 @@
         <v>31</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
@@ -1472,11 +1478,11 @@
         <v>34</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
@@ -1493,7 +1499,7 @@
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
@@ -1501,51 +1507,53 @@
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="C17:D18"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="C16:D16"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="B11:B15"/>
     <mergeCell ref="C11:C12"/>
@@ -1562,13 +1570,11 @@
     <mergeCell ref="C5:D7"/>
     <mergeCell ref="D11:D12"/>
     <mergeCell ref="C13:C15"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="C17:D18"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C24:E24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1588,7 +1594,7 @@
   <sheetData>
     <row r="1" spans="2:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="9" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -1596,7 +1602,7 @@
     </row>
     <row r="2" spans="2:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="9" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
@@ -1619,19 +1625,19 @@
         <v>4</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>96</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>100</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10"/>
@@ -1645,7 +1651,7 @@
     <row r="7" spans="2:5" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="9"/>
       <c r="C7" s="11" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D7" s="11"/>
       <c r="E7" s="10"/>
@@ -1655,17 +1661,17 @@
         <v>12</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="10" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="9"/>
       <c r="C9" s="11" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="10"/>
@@ -1673,7 +1679,7 @@
     <row r="10" spans="2:5" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="9"/>
       <c r="C10" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="10"/>
@@ -1683,13 +1689,13 @@
         <v>17</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
@@ -1721,17 +1727,17 @@
         <v>31</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D16" s="12"/>
       <c r="E16" s="10" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" spans="2:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="9"/>
       <c r="C17" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D17" s="11"/>
       <c r="E17" s="10"/>
@@ -1739,7 +1745,7 @@
     <row r="18" spans="2:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="9"/>
       <c r="C18" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D18" s="11"/>
       <c r="E18" s="10"/>
@@ -1749,7 +1755,7 @@
         <v>34</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="10"/>
@@ -1768,7 +1774,7 @@
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="9" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
@@ -1776,7 +1782,7 @@
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
@@ -1784,7 +1790,7 @@
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
@@ -1792,46 +1798,61 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="E11:E15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="C19:D20"/>
+    <mergeCell ref="E16:E20"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C27:E27"/>
     <mergeCell ref="B11:B15"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="B2:E2"/>
@@ -1845,24 +1866,9 @@
     <mergeCell ref="E8:E10"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="C19:D20"/>
-    <mergeCell ref="E16:E20"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C27:E27"/>
     <mergeCell ref="E4:E7"/>
     <mergeCell ref="C11:C15"/>
     <mergeCell ref="D11:D15"/>
-    <mergeCell ref="E11:E15"/>
-    <mergeCell ref="C17:D17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Docs/Characters.xlsx
+++ b/Docs/Characters.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Toddy" sheetId="1" r:id="rId1"/>
@@ -269,9 +269,6 @@
     <t>More boring units associated with fantasy, tries to keep balance between infantry and heavy units</t>
   </si>
   <si>
-    <t>Torch-bearer, Starving soldier, Goblin</t>
-  </si>
-  <si>
     <t>Red dragon, Rolling bastion</t>
   </si>
   <si>
@@ -372,6 +369,9 @@
   </si>
   <si>
     <t>[Galapo, Armo, Hazar, Boxor, Watt], [Tallyman, Forest mage/Plague mage]</t>
+  </si>
+  <si>
+    <t>Torch-bearer, Starving soldierm Abandoned soldier, Goblin</t>
   </si>
 </sst>
 </file>
@@ -755,13 +755,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:E24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.5546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="1.5703125" style="1" customWidth="1"/>
     <col min="2" max="3" width="24" style="1" customWidth="1"/>
-    <col min="4" max="4" width="48.21875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="42.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="1"/>
+    <col min="4" max="4" width="48.28515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="42.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -780,7 +780,7 @@
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
@@ -792,7 +792,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:5" ht="28.9" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
@@ -804,7 +804,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
         <v>4</v>
       </c>
@@ -816,7 +816,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="9"/>
       <c r="C6" s="9" t="s">
         <v>9</v>
@@ -824,7 +824,7 @@
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="9"/>
       <c r="C7" s="9" t="s">
         <v>11</v>
@@ -832,7 +832,7 @@
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
         <v>12</v>
       </c>
@@ -844,7 +844,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="9"/>
       <c r="C9" s="9" t="s">
         <v>15</v>
@@ -852,7 +852,7 @@
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="9"/>
       <c r="C10" s="9" t="s">
         <v>16</v>
@@ -860,7 +860,7 @@
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
     </row>
-    <row r="11" spans="2:5" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
         <v>17</v>
       </c>
@@ -874,7 +874,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" s="9"/>
       <c r="C12" s="10"/>
       <c r="D12" s="1" t="s">
@@ -882,7 +882,7 @@
       </c>
       <c r="E12" s="10"/>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="9"/>
       <c r="C13" s="1" t="s">
         <v>21</v>
@@ -894,7 +894,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="9"/>
       <c r="C14" s="1" t="s">
         <v>24</v>
@@ -906,7 +906,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="9"/>
       <c r="C15" s="1" t="s">
         <v>27</v>
@@ -918,7 +918,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:5" ht="28.9" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
         <v>31</v>
       </c>
@@ -930,7 +930,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
         <v>34</v>
       </c>
@@ -942,7 +942,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="9"/>
       <c r="C18" s="9" t="s">
         <v>37</v>
@@ -950,13 +950,13 @@
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
         <v>71</v>
       </c>
@@ -964,7 +964,7 @@
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
         <v>77</v>
       </c>
@@ -974,32 +974,32 @@
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
         <v>72</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
         <v>73</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
         <v>74</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
@@ -1042,24 +1042,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:E25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" customWidth="1"/>
-    <col min="3" max="3" width="38.77734375" customWidth="1"/>
+    <col min="1" max="1" width="2.7109375" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" customWidth="1"/>
+    <col min="3" max="3" width="38.7109375" customWidth="1"/>
     <col min="4" max="4" width="37" customWidth="1"/>
     <col min="5" max="5" width="66" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B1" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B2" s="9" t="s">
         <v>39</v>
       </c>
@@ -1067,7 +1067,7 @@
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:5" ht="43.15" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
@@ -1091,7 +1091,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
         <v>4</v>
       </c>
@@ -1103,19 +1103,19 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
         <v>12</v>
       </c>
@@ -1125,7 +1125,7 @@
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="9"/>
       <c r="C9" s="9" t="s">
         <v>45</v>
@@ -1133,7 +1133,7 @@
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="9"/>
       <c r="C10" s="9" t="s">
         <v>46</v>
@@ -1141,7 +1141,7 @@
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
         <v>17</v>
       </c>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="E11" s="9"/>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" s="9"/>
       <c r="C12" s="3" t="s">
         <v>48</v>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="E12" s="9"/>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="9"/>
       <c r="C13" s="1" t="s">
         <v>56</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="E13" s="9"/>
     </row>
-    <row r="14" spans="2:5" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:5" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="9"/>
       <c r="C14" s="1" t="s">
         <v>57</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="E14" s="10"/>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="9"/>
       <c r="C15" s="1" t="s">
         <v>58</v>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="E15" s="9"/>
     </row>
-    <row r="16" spans="2:5" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:5" ht="37.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
         <v>31</v>
       </c>
@@ -1203,7 +1203,7 @@
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
         <v>34</v>
       </c>
@@ -1213,19 +1213,19 @@
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B20" s="9" t="s">
         <v>71</v>
       </c>
@@ -1233,50 +1233,50 @@
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B21" s="6" t="s">
         <v>77</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B22" s="6" t="s">
         <v>72</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
     </row>
-    <row r="23" spans="2:5" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="9" t="s">
         <v>73</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
     </row>
-    <row r="24" spans="2:5" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:5" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="9"/>
       <c r="C24" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B25" s="6" t="s">
         <v>74</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
@@ -1318,16 +1318,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:E24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.5546875" customWidth="1"/>
-    <col min="2" max="2" width="30.77734375" customWidth="1"/>
-    <col min="3" max="3" width="30.88671875" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" customWidth="1"/>
-    <col min="5" max="5" width="27.5546875" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.85546875" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" customWidth="1"/>
+    <col min="5" max="5" width="27.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B1" s="9" t="s">
         <v>59</v>
       </c>
@@ -1335,7 +1335,7 @@
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B2" s="9" t="s">
         <v>66</v>
       </c>
@@ -1343,7 +1343,7 @@
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
@@ -1355,7 +1355,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:5" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:5" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
@@ -1367,7 +1367,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
         <v>4</v>
       </c>
@@ -1377,19 +1377,19 @@
       <c r="D5" s="9"/>
       <c r="E5" s="10"/>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="10"/>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="10"/>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
         <v>12</v>
       </c>
@@ -1401,7 +1401,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="9"/>
       <c r="C9" s="9" t="s">
         <v>63</v>
@@ -1409,7 +1409,7 @@
       <c r="D9" s="9"/>
       <c r="E9" s="10"/>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="9"/>
       <c r="C10" s="9" t="s">
         <v>64</v>
@@ -1417,7 +1417,7 @@
       <c r="D10" s="9"/>
       <c r="E10" s="10"/>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
         <v>17</v>
       </c>
@@ -1431,13 +1431,13 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="2:5" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" ht="67.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="9"/>
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="9"/>
       <c r="C13" s="9" t="s">
         <v>24</v>
@@ -1449,19 +1449,19 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
       <c r="D14" s="10"/>
       <c r="E14" s="9"/>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
       <c r="D15" s="10"/>
       <c r="E15" s="9"/>
     </row>
-    <row r="16" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
         <v>31</v>
       </c>
@@ -1473,7 +1473,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
         <v>34</v>
       </c>
@@ -1485,19 +1485,19 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B20" s="9" t="s">
         <v>71</v>
       </c>
@@ -1505,42 +1505,42 @@
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B21" s="6" t="s">
         <v>77</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B22" s="6" t="s">
         <v>72</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B23" s="6" t="s">
         <v>73</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B24" s="6" t="s">
         <v>74</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
@@ -1583,18 +1583,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:E28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.5546875" style="7" customWidth="1"/>
+    <col min="1" max="1" width="1.5703125" style="7" customWidth="1"/>
     <col min="2" max="3" width="24" style="7" customWidth="1"/>
-    <col min="4" max="4" width="48.21875" style="7" customWidth="1"/>
-    <col min="5" max="5" width="42.44140625" style="7" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="7"/>
+    <col min="4" max="4" width="48.28515625" style="7" customWidth="1"/>
+    <col min="5" max="5" width="42.42578125" style="7" customWidth="1"/>
+    <col min="6" max="16384" width="8.85546875" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -1602,13 +1602,13 @@
     </row>
     <row r="2" spans="2:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
@@ -1620,175 +1620,175 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:5" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:5" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="9" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="9" t="s">
-        <v>92</v>
-      </c>
       <c r="C5" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10"/>
     </row>
-    <row r="6" spans="2:5" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="10"/>
     </row>
-    <row r="7" spans="2:5" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="9"/>
       <c r="C7" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D7" s="11"/>
       <c r="E7" s="10"/>
     </row>
-    <row r="8" spans="2:5" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="10" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="9"/>
       <c r="C9" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="10"/>
     </row>
-    <row r="10" spans="2:5" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="9"/>
       <c r="C10" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="10"/>
     </row>
-    <row r="11" spans="2:5" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" s="9"/>
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="9"/>
       <c r="C13" s="10"/>
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="9"/>
       <c r="C14" s="10"/>
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="9"/>
       <c r="C15" s="10"/>
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
     </row>
-    <row r="16" spans="2:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D16" s="12"/>
       <c r="E16" s="10" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="9"/>
       <c r="C17" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D17" s="11"/>
       <c r="E17" s="10"/>
     </row>
-    <row r="18" spans="2:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="9"/>
       <c r="C18" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D18" s="11"/>
       <c r="E18" s="10"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
         <v>34</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="10"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="10"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B22" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B23" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B24" s="9" t="s">
         <v>71</v>
       </c>
@@ -1796,49 +1796,48 @@
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B25" s="7" t="s">
         <v>77</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B26" s="7" t="s">
         <v>72</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27" s="7" t="s">
         <v>73</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B28" s="7" t="s">
         <v>74</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="E11:E15"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="C28:E28"/>
     <mergeCell ref="B22:E22"/>
@@ -1853,7 +1852,6 @@
     <mergeCell ref="C25:E25"/>
     <mergeCell ref="C26:E26"/>
     <mergeCell ref="C27:E27"/>
-    <mergeCell ref="B11:B15"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="C3:D3"/>
@@ -1861,14 +1859,16 @@
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C5:D6"/>
+    <mergeCell ref="E4:E7"/>
+    <mergeCell ref="C11:C15"/>
+    <mergeCell ref="D11:D15"/>
     <mergeCell ref="B8:B10"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="E8:E10"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E4:E7"/>
-    <mergeCell ref="C11:C15"/>
-    <mergeCell ref="D11:D15"/>
+    <mergeCell ref="E11:E15"/>
+    <mergeCell ref="B11:B15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Docs/Characters.xlsx
+++ b/Docs/Characters.xlsx
@@ -272,9 +272,6 @@
     <t>Red dragon, Rolling bastion</t>
   </si>
   <si>
-    <t>Suspiciously tall goblin, cavebilly, lightning mage, crude mage</t>
-  </si>
-  <si>
     <t>Weirdest units, often rely on combinations with each other and spawn next to each other</t>
   </si>
   <si>
@@ -371,7 +368,10 @@
     <t>[Galapo, Armo, Hazar, Boxor, Watt], [Tallyman, Forest mage/Plague mage]</t>
   </si>
   <si>
-    <t>Torch-bearer, Starving soldierm Abandoned soldier, Goblin</t>
+    <t>2 {Suspiciously tall goblin}, cavebilly, lightning mage, crude mage</t>
+  </si>
+  <si>
+    <t>2 {Torch-bearer}, Starving soldierm Abandoned soldier, Goblin</t>
   </si>
 </sst>
 </file>
@@ -989,7 +989,7 @@
         <v>73</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
@@ -1006,14 +1006,11 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="B11:B15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="E5:E7"/>
@@ -1028,11 +1025,14 @@
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="B11:B15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1053,7 +1053,7 @@
   <sheetData>
     <row r="1" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B1" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -1238,7 +1238,7 @@
         <v>77</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
@@ -1248,7 +1248,7 @@
         <v>72</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
@@ -1258,7 +1258,7 @@
         <v>73</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
@@ -1266,7 +1266,7 @@
     <row r="24" spans="2:5" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="9"/>
       <c r="C24" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
@@ -1276,20 +1276,19 @@
         <v>74</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="C5:D7"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C24:E24"/>
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="D12:E12"/>
@@ -1304,12 +1303,13 @@
     <mergeCell ref="C17:E18"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="C5:D7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1510,7 +1510,7 @@
         <v>77</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
@@ -1520,7 +1520,7 @@
         <v>72</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
@@ -1530,7 +1530,7 @@
         <v>73</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
@@ -1540,20 +1540,18 @@
         <v>74</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="C17:D18"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C24:E24"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="B11:B15"/>
     <mergeCell ref="C11:C12"/>
@@ -1570,11 +1568,13 @@
     <mergeCell ref="C5:D7"/>
     <mergeCell ref="D11:D12"/>
     <mergeCell ref="C13:C15"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="C17:D18"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="C16:D16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1594,7 +1594,7 @@
   <sheetData>
     <row r="1" spans="2:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="2" spans="2:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
@@ -1625,19 +1625,19 @@
         <v>4</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10"/>
@@ -1651,7 +1651,7 @@
     <row r="7" spans="2:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="9"/>
       <c r="C7" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D7" s="11"/>
       <c r="E7" s="10"/>
@@ -1661,17 +1661,17 @@
         <v>12</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="9"/>
       <c r="C9" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="10"/>
@@ -1679,7 +1679,7 @@
     <row r="10" spans="2:5" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="9"/>
       <c r="C10" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="10"/>
@@ -1689,13 +1689,13 @@
         <v>17</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
@@ -1727,17 +1727,17 @@
         <v>31</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D16" s="12"/>
       <c r="E16" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="2:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="9"/>
       <c r="C17" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D17" s="11"/>
       <c r="E17" s="10"/>
@@ -1745,7 +1745,7 @@
     <row r="18" spans="2:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="9"/>
       <c r="C18" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D18" s="11"/>
       <c r="E18" s="10"/>
@@ -1755,7 +1755,7 @@
         <v>34</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="10"/>
@@ -1774,7 +1774,7 @@
     </row>
     <row r="22" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B22" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
@@ -1782,7 +1782,7 @@
     </row>
     <row r="23" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B23" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
@@ -1801,7 +1801,7 @@
         <v>77</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
@@ -1811,7 +1811,7 @@
         <v>72</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
@@ -1821,7 +1821,7 @@
         <v>73</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
@@ -1838,6 +1838,23 @@
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="C11:C15"/>
+    <mergeCell ref="D11:D15"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E11:E15"/>
+    <mergeCell ref="B11:B15"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C5:D6"/>
+    <mergeCell ref="E4:E7"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="C28:E28"/>
     <mergeCell ref="B22:E22"/>
@@ -1852,23 +1869,6 @@
     <mergeCell ref="C25:E25"/>
     <mergeCell ref="C26:E26"/>
     <mergeCell ref="C27:E27"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C5:D6"/>
-    <mergeCell ref="E4:E7"/>
-    <mergeCell ref="C11:C15"/>
-    <mergeCell ref="D11:D15"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E11:E15"/>
-    <mergeCell ref="B11:B15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Docs/Characters.xlsx
+++ b/Docs/Characters.xlsx
@@ -368,10 +368,10 @@
     <t>[Galapo, Armo, Hazar, Boxor, Watt], [Tallyman, Forest mage/Plague mage]</t>
   </si>
   <si>
-    <t>2 {Suspiciously tall goblin}, cavebilly, lightning mage, crude mage</t>
-  </si>
-  <si>
-    <t>2 {Torch-bearer}, Starving soldierm Abandoned soldier, Goblin</t>
+    <t>2 {Suspiciously tall goblin}, roach mage, cavebilly, lightning mage, crude mage, water mage</t>
+  </si>
+  <si>
+    <t>2 {Torch-bearer}, Starving soldier, Abandoned soldier, Goblin</t>
   </si>
 </sst>
 </file>
@@ -403,7 +403,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -411,11 +411,91 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -452,6 +532,33 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -950,67 +1057,70 @@
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
     </row>
-    <row r="19" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="15"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="18"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="18"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B24" s="1" t="s">
+      <c r="D23" s="17"/>
+      <c r="E23" s="18"/>
+    </row>
+    <row r="24" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="B11:B15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="E5:E7"/>
@@ -1025,14 +1135,11 @@
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="B11:B15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1283,12 +1390,13 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="C5:D7"/>
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="D12:E12"/>
@@ -1303,13 +1411,12 @@
     <mergeCell ref="C17:E18"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="C9:E9"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="C5:D7"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C24:E24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1547,11 +1654,13 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="C17:D18"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="C16:D16"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="B11:B15"/>
     <mergeCell ref="C11:C12"/>
@@ -1568,13 +1677,11 @@
     <mergeCell ref="C5:D7"/>
     <mergeCell ref="D11:D12"/>
     <mergeCell ref="C13:C15"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="C17:D18"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C24:E24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1838,23 +1945,6 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="C11:C15"/>
-    <mergeCell ref="D11:D15"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E11:E15"/>
-    <mergeCell ref="B11:B15"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C5:D6"/>
-    <mergeCell ref="E4:E7"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="C28:E28"/>
     <mergeCell ref="B22:E22"/>
@@ -1869,6 +1959,23 @@
     <mergeCell ref="C25:E25"/>
     <mergeCell ref="C26:E26"/>
     <mergeCell ref="C27:E27"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C5:D6"/>
+    <mergeCell ref="E4:E7"/>
+    <mergeCell ref="C11:C15"/>
+    <mergeCell ref="D11:D15"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E11:E15"/>
+    <mergeCell ref="B11:B15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Docs/Characters.xlsx
+++ b/Docs/Characters.xlsx
@@ -7,17 +7,18 @@
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
-    <sheet name="Toddy" sheetId="1" r:id="rId1"/>
-    <sheet name="Fabulous Flask" sheetId="2" r:id="rId2"/>
-    <sheet name="Topol" sheetId="3" r:id="rId3"/>
-    <sheet name="Boss 1" sheetId="4" r:id="rId4"/>
+    <sheet name="Emi" sheetId="5" r:id="rId1"/>
+    <sheet name="Toddy" sheetId="1" r:id="rId2"/>
+    <sheet name="Fabulous Flask" sheetId="2" r:id="rId3"/>
+    <sheet name="Topol" sheetId="3" r:id="rId4"/>
+    <sheet name="Boss 1" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="143">
   <si>
     <t>Toddy/Knight/Boris</t>
   </si>
@@ -372,6 +373,93 @@
   </si>
   <si>
     <t>2 {Torch-bearer}, Starving soldier, Abandoned soldier, Goblin</t>
+  </si>
+  <si>
+    <t>[Shiraishi] Emi</t>
+  </si>
+  <si>
+    <t>Otherworldly student, a slapdash scholar</t>
+  </si>
+  <si>
+    <t>(Japanese)Ohhh, I'm running out of time</t>
+  </si>
+  <si>
+    <t>I'm so tired…</t>
+  </si>
+  <si>
+    <t>Another essay…</t>
+  </si>
+  <si>
+    <t>Ohhhh…</t>
+  </si>
+  <si>
+    <t>This makes no sense…</t>
+  </si>
+  <si>
+    <t>Yeah yeah, hold on a second</t>
+  </si>
+  <si>
+    <t>Stack of papers on the side</t>
+  </si>
+  <si>
+    <t>Continues tapping on the typewriter</t>
+  </si>
+  <si>
+    <t>A paper flies out of the stack</t>
+  </si>
+  <si>
+    <t>Typewriter</t>
+  </si>
+  <si>
+    <t>Typewriter ting</t>
+  </si>
+  <si>
+    <t>Clothes</t>
+  </si>
+  <si>
+    <t>Typewriter slightly shifts</t>
+  </si>
+  <si>
+    <t>Paper shuffle</t>
+  </si>
+  <si>
+    <t>Stars inside swirl a little</t>
+  </si>
+  <si>
+    <t>Vortex sound</t>
+  </si>
+  <si>
+    <t>Okay, this report done. I'm not done though!</t>
+  </si>
+  <si>
+    <t>Makes the typerwriter disappear, gets papers and stands up to leave the portal. Quickly turns to say the last line.</t>
+  </si>
+  <si>
+    <t>On to the next</t>
+  </si>
+  <si>
+    <t>Makes the typerwriter disappear, gets papers and stands up to leave the portal.</t>
+  </si>
+  <si>
+    <t>Okaaaay…</t>
+  </si>
+  <si>
+    <t>Glass cannon and fast units</t>
+  </si>
+  <si>
+    <t>Appears through Astel-like teleport effect with papers in hands. Walks a bit. Sists down and teleports the typewriter in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appears through Astel-like teleport effect with papers in hands directly in front of table. Sists down and teleports the typewriter in </t>
+  </si>
+  <si>
+    <t>2 {Spark}, 2 {Crystal warrior}, 2 {Bombshroom}</t>
+  </si>
+  <si>
+    <t>Conductor, Battering boar, Sour snail, Living olive, Corn knight, dwarven eliminator</t>
+  </si>
+  <si>
+    <t>Moving sandcastle, Suspicious dragon</t>
   </si>
 </sst>
 </file>
@@ -495,7 +583,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -527,10 +615,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -542,16 +636,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
@@ -559,6 +647,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -861,6 +955,285 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:E25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.5703125" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="4" max="4" width="22.42578125" customWidth="1"/>
+    <col min="5" max="5" width="63.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B2" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B3" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B4" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="13"/>
+      <c r="E4" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B5" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D5" s="13"/>
+      <c r="E5" s="10" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B6" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="D6" s="13"/>
+      <c r="E6" s="14" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B7" s="13"/>
+      <c r="C7" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="D7" s="13"/>
+      <c r="E7" s="14"/>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="14"/>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="13"/>
+      <c r="C10" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B11" s="13"/>
+      <c r="C11" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B12" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B13" s="13"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="14"/>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B14" s="13"/>
+      <c r="C14" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="E14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B15" s="13"/>
+      <c r="C15" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+    </row>
+    <row r="17" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B17" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="D17" s="13"/>
+      <c r="E17" s="10" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B18" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="D18" s="13"/>
+      <c r="E18" s="14" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B19" s="13"/>
+      <c r="C19" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="D19" s="13"/>
+      <c r="E19" s="14"/>
+    </row>
+    <row r="20" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B21" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="17"/>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B22" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="D22" s="18"/>
+      <c r="E22" s="19"/>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B23" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="D23" s="18"/>
+      <c r="E23" s="19"/>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B24" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="D24" s="18"/>
+      <c r="E24" s="19"/>
+    </row>
+    <row r="25" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="D25" s="20"/>
+      <c r="E25" s="21"/>
+    </row>
+  </sheetData>
+  <mergeCells count="30">
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:E24"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -872,29 +1245,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
     </row>
     <row r="2" spans="2:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
     </row>
     <row r="3" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="9"/>
+      <c r="D3" s="13"/>
       <c r="E3" s="1" t="s">
         <v>2</v>
       </c>
@@ -903,94 +1276,94 @@
       <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="9"/>
+      <c r="D4" s="13"/>
       <c r="E4" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9" t="s">
+      <c r="D5" s="13"/>
+      <c r="E5" s="13" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6" s="9"/>
-      <c r="C6" s="9" t="s">
+      <c r="B6" s="13"/>
+      <c r="C6" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B7" s="9"/>
-      <c r="C7" s="9" t="s">
+      <c r="B7" s="13"/>
+      <c r="C7" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9" t="s">
+      <c r="D8" s="13"/>
+      <c r="E8" s="13" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="9"/>
-      <c r="C9" s="9" t="s">
+      <c r="B9" s="13"/>
+      <c r="C9" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="9"/>
-      <c r="C10" s="9" t="s">
+      <c r="B10" s="13"/>
+      <c r="C10" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
     </row>
     <row r="11" spans="2:5" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="14" t="s">
         <v>19</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B12" s="9"/>
-      <c r="C12" s="10"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="14"/>
       <c r="D12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="10"/>
+      <c r="E12" s="14"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B13" s="9"/>
+      <c r="B13" s="13"/>
       <c r="C13" s="1" t="s">
         <v>21</v>
       </c>
@@ -1002,7 +1375,7 @@
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B14" s="9"/>
+      <c r="B14" s="13"/>
       <c r="C14" s="1" t="s">
         <v>24</v>
       </c>
@@ -1014,7 +1387,7 @@
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B15" s="9"/>
+      <c r="B15" s="13"/>
       <c r="C15" s="1" t="s">
         <v>27</v>
       </c>
@@ -1025,37 +1398,37 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="2:5" ht="28.9" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="9"/>
+      <c r="D16" s="13"/>
       <c r="E16" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9" t="s">
+      <c r="D17" s="13"/>
+      <c r="E17" s="13" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B18" s="9"/>
-      <c r="C18" s="9" t="s">
+      <c r="B18" s="13"/>
+      <c r="C18" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
     </row>
     <row r="19" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="8"/>
@@ -1064,45 +1437,45 @@
       <c r="E19" s="8"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="15"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="17"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D21" s="17"/>
-      <c r="E21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="19"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="D22" s="17"/>
-      <c r="E22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="19"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C23" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="D23" s="17"/>
-      <c r="E23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="19"/>
     </row>
     <row r="24" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="19" t="s">
+      <c r="B24" s="12" t="s">
         <v>74</v>
       </c>
       <c r="C24" s="20" t="s">
@@ -1113,14 +1486,11 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="B11:B15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="E5:E7"/>
@@ -1135,18 +1505,21 @@
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="B11:B15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:E25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1159,29 +1532,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
     </row>
     <row r="2" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
     </row>
     <row r="3" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="9"/>
+      <c r="D3" s="13"/>
       <c r="E3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1190,141 +1563,141 @@
       <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="10"/>
+      <c r="D4" s="14"/>
       <c r="E4" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9" t="s">
+      <c r="D5" s="13"/>
+      <c r="E5" s="13" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="9"/>
-      <c r="C9" s="9" t="s">
+      <c r="B9" s="13"/>
+      <c r="C9" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="9"/>
-      <c r="C10" s="9" t="s">
+      <c r="B10" s="13"/>
+      <c r="C10" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="13" t="s">
         <v>17</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="E11" s="9"/>
+      <c r="E11" s="13"/>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B12" s="9"/>
+      <c r="B12" s="13"/>
       <c r="C12" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="E12" s="9"/>
+      <c r="E12" s="13"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B13" s="9"/>
+      <c r="B13" s="13"/>
       <c r="C13" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="9"/>
+      <c r="E13" s="13"/>
     </row>
     <row r="14" spans="2:5" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="9"/>
+      <c r="B14" s="13"/>
       <c r="C14" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="E14" s="10"/>
+      <c r="E14" s="14"/>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B15" s="9"/>
+      <c r="B15" s="13"/>
       <c r="C15" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="9"/>
+      <c r="E15" s="13"/>
     </row>
     <row r="16" spans="2:5" ht="37.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
     </row>
     <row r="19" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B19" s="8"/>
@@ -1333,70 +1706,69 @@
       <c r="E19" s="8"/>
     </row>
     <row r="20" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
     </row>
     <row r="21" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B21" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
     </row>
     <row r="22" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B22" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
     </row>
     <row r="23" spans="2:5" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
     </row>
     <row r="24" spans="2:5" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="9"/>
-      <c r="C24" s="9" t="s">
+      <c r="B24" s="13"/>
+      <c r="C24" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
     </row>
     <row r="25" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B25" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="C5:D7"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C24:E24"/>
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="D12:E12"/>
@@ -1411,18 +1783,19 @@
     <mergeCell ref="C17:E18"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="C5:D7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:E24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1435,29 +1808,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
     </row>
     <row r="2" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
     </row>
     <row r="3" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="9"/>
+      <c r="D3" s="13"/>
       <c r="E3" s="4" t="s">
         <v>2</v>
       </c>
@@ -1466,137 +1839,137 @@
       <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10" t="s">
+      <c r="D4" s="14"/>
+      <c r="E4" s="14" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="10"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="14"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="10"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="14"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="10"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="14"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="10" t="s">
+      <c r="D8" s="13"/>
+      <c r="E8" s="14" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="9"/>
-      <c r="C9" s="9" t="s">
+      <c r="B9" s="13"/>
+      <c r="C9" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="10"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="14"/>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="9"/>
-      <c r="C10" s="9" t="s">
+      <c r="B10" s="13"/>
+      <c r="C10" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="10"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="14"/>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="14" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="12" spans="2:5" ht="67.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="9"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B13" s="9"/>
-      <c r="C13" s="9" t="s">
+      <c r="B13" s="13"/>
+      <c r="C13" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="13" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="9"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="13"/>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="9"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="13"/>
     </row>
     <row r="16" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="D16" s="10"/>
+      <c r="D16" s="14"/>
       <c r="E16" s="5" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9" t="s">
+      <c r="D17" s="13"/>
+      <c r="E17" s="13" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
     </row>
     <row r="19" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B19" s="8"/>
@@ -1605,62 +1978,60 @@
       <c r="E19" s="8"/>
     </row>
     <row r="20" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
     </row>
     <row r="21" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B21" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
     </row>
     <row r="22" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B22" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
     </row>
     <row r="23" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B23" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
     </row>
     <row r="24" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B24" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="C17:D18"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C24:E24"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="B11:B15"/>
     <mergeCell ref="C11:C12"/>
@@ -1677,17 +2048,19 @@
     <mergeCell ref="C5:D7"/>
     <mergeCell ref="D11:D12"/>
     <mergeCell ref="C13:C15"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="C17:D18"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="C16:D16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:E28"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1700,29 +2073,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
     </row>
     <row r="2" spans="2:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
     </row>
     <row r="3" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="9"/>
+      <c r="D3" s="13"/>
       <c r="E3" s="7" t="s">
         <v>2</v>
       </c>
@@ -1731,147 +2104,147 @@
       <c r="B4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10" t="s">
+      <c r="D4" s="14"/>
+      <c r="E4" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="10"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="14"/>
     </row>
     <row r="6" spans="2:5" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="10"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="14"/>
     </row>
     <row r="7" spans="2:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="9"/>
-      <c r="C7" s="11" t="s">
+      <c r="B7" s="13"/>
+      <c r="C7" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="D7" s="11"/>
-      <c r="E7" s="10"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="14"/>
     </row>
     <row r="8" spans="2:5" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="10" t="s">
+      <c r="D8" s="22"/>
+      <c r="E8" s="14" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="9" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="9"/>
-      <c r="C9" s="11" t="s">
+      <c r="B9" s="13"/>
+      <c r="C9" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="10"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="14"/>
     </row>
     <row r="10" spans="2:5" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="9"/>
-      <c r="C10" s="11" t="s">
+      <c r="B10" s="13"/>
+      <c r="C10" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="10"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="14"/>
     </row>
     <row r="11" spans="2:5" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="14" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B12" s="9"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B13" s="9"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B14" s="9"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B15" s="9"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
     </row>
     <row r="16" spans="2:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="D16" s="12"/>
-      <c r="E16" s="10" t="s">
+      <c r="D16" s="23"/>
+      <c r="E16" s="14" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="17" spans="2:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="9"/>
-      <c r="C17" s="11" t="s">
+      <c r="B17" s="13"/>
+      <c r="C17" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="D17" s="11"/>
-      <c r="E17" s="10"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="14"/>
     </row>
     <row r="18" spans="2:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="9"/>
-      <c r="C18" s="11" t="s">
+      <c r="B18" s="13"/>
+      <c r="C18" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="D18" s="11"/>
-      <c r="E18" s="10"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="14"/>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="D19" s="9"/>
-      <c r="E19" s="10"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="14"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="10"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="14"/>
     </row>
     <row r="21" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B21" s="8"/>
@@ -1880,71 +2253,88 @@
       <c r="E21" s="8"/>
     </row>
     <row r="22" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
     </row>
     <row r="23" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
     </row>
     <row r="24" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
     </row>
     <row r="25" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B25" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
     </row>
     <row r="26" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B26" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B28" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="C11:C15"/>
+    <mergeCell ref="D11:D15"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E11:E15"/>
+    <mergeCell ref="B11:B15"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C5:D6"/>
+    <mergeCell ref="E4:E7"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="C28:E28"/>
     <mergeCell ref="B22:E22"/>
@@ -1959,23 +2349,6 @@
     <mergeCell ref="C25:E25"/>
     <mergeCell ref="C26:E26"/>
     <mergeCell ref="C27:E27"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C5:D6"/>
-    <mergeCell ref="E4:E7"/>
-    <mergeCell ref="C11:C15"/>
-    <mergeCell ref="D11:D15"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E11:E15"/>
-    <mergeCell ref="B11:B15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Docs/Characters.xlsx
+++ b/Docs/Characters.xlsx
@@ -456,10 +456,10 @@
     <t>2 {Spark}, 2 {Crystal warrior}, 2 {Bombshroom}</t>
   </si>
   <si>
-    <t>Conductor, Battering boar, Sour snail, Living olive, Corn knight, dwarven eliminator</t>
-  </si>
-  <si>
     <t>Moving sandcastle, Suspicious dragon</t>
+  </si>
+  <si>
+    <t>Conductor, Battering boar, Sour snail, Living olive, Corn knight, dwarven eliminator, Siren</t>
   </si>
 </sst>
 </file>
@@ -621,6 +621,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -634,18 +646,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -966,29 +966,29 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="13"/>
+      <c r="D4" s="17"/>
       <c r="E4" s="9" t="s">
         <v>2</v>
       </c>
@@ -997,90 +997,90 @@
       <c r="B5" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="D5" s="13"/>
+      <c r="D5" s="17"/>
       <c r="E5" s="10" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="14" t="s">
+      <c r="D6" s="17"/>
+      <c r="E6" s="18" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B7" s="13"/>
-      <c r="C7" s="13" t="s">
+      <c r="B7" s="17"/>
+      <c r="C7" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="D7" s="13"/>
-      <c r="E7" s="14"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="18"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="14"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="18"/>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13" t="s">
+      <c r="D9" s="17"/>
+      <c r="E9" s="17" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="13"/>
-      <c r="C10" s="13" t="s">
+      <c r="B10" s="17"/>
+      <c r="C10" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="13"/>
-      <c r="C11" s="13" t="s">
+      <c r="B11" s="17"/>
+      <c r="C11" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="18" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B13" s="13"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="14"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="18"/>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B14" s="13"/>
+      <c r="B14" s="17"/>
       <c r="C14" s="9" t="s">
         <v>125</v>
       </c>
@@ -1092,54 +1092,54 @@
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B15" s="13"/>
-      <c r="C15" s="13" t="s">
+      <c r="B15" s="17"/>
+      <c r="C15" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="17" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
     </row>
     <row r="17" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D17" s="13"/>
+      <c r="D17" s="17"/>
       <c r="E17" s="10" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="D18" s="13"/>
-      <c r="E18" s="14" t="s">
+      <c r="D18" s="17"/>
+      <c r="E18" s="18" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B19" s="13"/>
-      <c r="C19" s="13" t="s">
+      <c r="B19" s="17"/>
+      <c r="C19" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="D19" s="13"/>
-      <c r="E19" s="14"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="18"/>
     </row>
     <row r="20" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="8"/>
@@ -1148,70 +1148,55 @@
       <c r="E20" s="8"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="17"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="21"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="D22" s="18"/>
-      <c r="E22" s="19"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="14"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="18" t="s">
+      <c r="C23" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="D23" s="18"/>
-      <c r="E23" s="19"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="14"/>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="C24" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="D24" s="18"/>
-      <c r="E24" s="19"/>
+      <c r="C24" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="D24" s="13"/>
+      <c r="E24" s="14"/>
     </row>
     <row r="25" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="C25" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="D25" s="20"/>
-      <c r="E25" s="21"/>
+      <c r="C25" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="D25" s="15"/>
+      <c r="E25" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="B21:E21"/>
     <mergeCell ref="B12:B16"/>
     <mergeCell ref="C12:C13"/>
     <mergeCell ref="E12:E13"/>
@@ -1227,6 +1212,21 @@
     <mergeCell ref="E9:E11"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C11:D11"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="C17:D17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1245,29 +1245,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
     </row>
     <row r="2" spans="2:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
     </row>
     <row r="3" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="13"/>
+      <c r="D3" s="17"/>
       <c r="E3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1276,94 +1276,94 @@
       <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="13"/>
+      <c r="D4" s="17"/>
       <c r="E4" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13" t="s">
+      <c r="D5" s="17"/>
+      <c r="E5" s="17" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6" s="13"/>
-      <c r="C6" s="13" t="s">
+      <c r="B6" s="17"/>
+      <c r="C6" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B7" s="13"/>
-      <c r="C7" s="13" t="s">
+      <c r="B7" s="17"/>
+      <c r="C7" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13" t="s">
+      <c r="D8" s="17"/>
+      <c r="E8" s="17" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="13"/>
-      <c r="C9" s="13" t="s">
+      <c r="B9" s="17"/>
+      <c r="C9" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="13"/>
-      <c r="C10" s="13" t="s">
+      <c r="B10" s="17"/>
+      <c r="C10" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
     </row>
     <row r="11" spans="2:5" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="18" t="s">
         <v>19</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="18" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B12" s="13"/>
-      <c r="C12" s="14"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="18"/>
       <c r="D12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="14"/>
+      <c r="E12" s="18"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B13" s="13"/>
+      <c r="B13" s="17"/>
       <c r="C13" s="1" t="s">
         <v>21</v>
       </c>
@@ -1375,7 +1375,7 @@
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B14" s="13"/>
+      <c r="B14" s="17"/>
       <c r="C14" s="1" t="s">
         <v>24</v>
       </c>
@@ -1387,7 +1387,7 @@
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B15" s="13"/>
+      <c r="B15" s="17"/>
       <c r="C15" s="1" t="s">
         <v>27</v>
       </c>
@@ -1402,33 +1402,33 @@
       <c r="B16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="13"/>
+      <c r="D16" s="17"/>
       <c r="E16" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13" t="s">
+      <c r="D17" s="17"/>
+      <c r="E17" s="17" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B18" s="13"/>
-      <c r="C18" s="13" t="s">
+      <c r="B18" s="17"/>
+      <c r="C18" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
     </row>
     <row r="19" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="8"/>
@@ -1437,60 +1437,63 @@
       <c r="E19" s="8"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="17"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="21"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="D21" s="18"/>
-      <c r="E21" s="19"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="14"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="D22" s="18"/>
-      <c r="E22" s="19"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="14"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="18" t="s">
+      <c r="C23" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="D23" s="18"/>
-      <c r="E23" s="19"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="14"/>
     </row>
     <row r="24" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="C24" s="20" t="s">
+      <c r="C24" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="D24" s="20"/>
-      <c r="E24" s="21"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="B11:B15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="E5:E7"/>
@@ -1505,14 +1508,11 @@
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="B11:B15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1532,29 +1532,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
     </row>
     <row r="2" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
     </row>
     <row r="3" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="13"/>
+      <c r="D3" s="17"/>
       <c r="E3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1563,141 +1563,141 @@
       <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="14"/>
+      <c r="D4" s="18"/>
       <c r="E4" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13" t="s">
+      <c r="D5" s="17"/>
+      <c r="E5" s="17" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="13"/>
-      <c r="C9" s="13" t="s">
+      <c r="B9" s="17"/>
+      <c r="C9" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="13"/>
-      <c r="C10" s="13" t="s">
+      <c r="B10" s="17"/>
+      <c r="C10" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="17" t="s">
         <v>17</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="E11" s="13"/>
+      <c r="E11" s="17"/>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B12" s="13"/>
+      <c r="B12" s="17"/>
       <c r="C12" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="E12" s="13"/>
+      <c r="E12" s="17"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B13" s="13"/>
+      <c r="B13" s="17"/>
       <c r="C13" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="13"/>
+      <c r="E13" s="17"/>
     </row>
     <row r="14" spans="2:5" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="13"/>
+      <c r="B14" s="17"/>
       <c r="C14" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="E14" s="14"/>
+      <c r="E14" s="18"/>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B15" s="13"/>
+      <c r="B15" s="17"/>
       <c r="C15" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="13"/>
+      <c r="E15" s="17"/>
     </row>
     <row r="16" spans="2:5" ht="37.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
     </row>
     <row r="19" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B19" s="8"/>
@@ -1706,69 +1706,70 @@
       <c r="E19" s="8"/>
     </row>
     <row r="20" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
     </row>
     <row r="21" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B21" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
     </row>
     <row r="22" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B22" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
     </row>
     <row r="23" spans="2:5" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
     </row>
     <row r="24" spans="2:5" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="13"/>
-      <c r="C24" s="13" t="s">
+      <c r="B24" s="17"/>
+      <c r="C24" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
     </row>
     <row r="25" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B25" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="C5:D7"/>
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="D12:E12"/>
@@ -1783,13 +1784,12 @@
     <mergeCell ref="C17:E18"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="C9:E9"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="C5:D7"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C24:E24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1808,29 +1808,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
     </row>
     <row r="2" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
     </row>
     <row r="3" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="13"/>
+      <c r="D3" s="17"/>
       <c r="E3" s="4" t="s">
         <v>2</v>
       </c>
@@ -1839,137 +1839,137 @@
       <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14" t="s">
+      <c r="D4" s="18"/>
+      <c r="E4" s="18" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="14"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="18"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="14"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="18"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="14"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="18"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="D8" s="13"/>
-      <c r="E8" s="14" t="s">
+      <c r="D8" s="17"/>
+      <c r="E8" s="18" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="13"/>
-      <c r="C9" s="13" t="s">
+      <c r="B9" s="17"/>
+      <c r="C9" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="14"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="18"/>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="13"/>
-      <c r="C10" s="13" t="s">
+      <c r="B10" s="17"/>
+      <c r="C10" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="14"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="18"/>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="18" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="12" spans="2:5" ht="67.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="13"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B13" s="13"/>
-      <c r="C13" s="13" t="s">
+      <c r="B13" s="17"/>
+      <c r="C13" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="17" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="13"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="17"/>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="13"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="17"/>
     </row>
     <row r="16" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D16" s="14"/>
+      <c r="D16" s="18"/>
       <c r="E16" s="5" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13" t="s">
+      <c r="D17" s="17"/>
+      <c r="E17" s="17" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
     </row>
     <row r="19" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B19" s="8"/>
@@ -1978,60 +1978,62 @@
       <c r="E19" s="8"/>
     </row>
     <row r="20" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
     </row>
     <row r="21" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B21" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
     </row>
     <row r="22" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B22" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
     </row>
     <row r="23" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B23" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
     </row>
     <row r="24" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B24" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="C17:D18"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="C16:D16"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="B11:B15"/>
     <mergeCell ref="C11:C12"/>
@@ -2048,13 +2050,11 @@
     <mergeCell ref="C5:D7"/>
     <mergeCell ref="D11:D12"/>
     <mergeCell ref="C13:C15"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="C17:D18"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C24:E24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2073,29 +2073,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
     </row>
     <row r="2" spans="2:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
     </row>
     <row r="3" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="13"/>
+      <c r="D3" s="17"/>
       <c r="E3" s="7" t="s">
         <v>2</v>
       </c>
@@ -2104,147 +2104,147 @@
       <c r="B4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14" t="s">
+      <c r="D4" s="18"/>
+      <c r="E4" s="18" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="17" t="s">
         <v>90</v>
       </c>
       <c r="C5" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="14"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="18"/>
     </row>
     <row r="6" spans="2:5" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="14"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="18"/>
     </row>
     <row r="7" spans="2:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="13"/>
+      <c r="B7" s="17"/>
       <c r="C7" s="22" t="s">
         <v>95</v>
       </c>
       <c r="D7" s="22"/>
-      <c r="E7" s="14"/>
+      <c r="E7" s="18"/>
     </row>
     <row r="8" spans="2:5" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="17" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>96</v>
       </c>
       <c r="D8" s="22"/>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="18" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="9" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="13"/>
+      <c r="B9" s="17"/>
       <c r="C9" s="22" t="s">
         <v>97</v>
       </c>
       <c r="D9" s="22"/>
-      <c r="E9" s="14"/>
+      <c r="E9" s="18"/>
     </row>
     <row r="10" spans="2:5" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="13"/>
+      <c r="B10" s="17"/>
       <c r="C10" s="22" t="s">
         <v>100</v>
       </c>
       <c r="D10" s="22"/>
-      <c r="E10" s="14"/>
+      <c r="E10" s="18"/>
     </row>
     <row r="11" spans="2:5" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="18" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B12" s="13"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B13" s="13"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B14" s="13"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B15" s="13"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
     </row>
     <row r="16" spans="2:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="17" t="s">
         <v>31</v>
       </c>
       <c r="C16" s="23" t="s">
         <v>98</v>
       </c>
       <c r="D16" s="23"/>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="18" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="17" spans="2:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="13"/>
+      <c r="B17" s="17"/>
       <c r="C17" s="22" t="s">
         <v>99</v>
       </c>
       <c r="D17" s="22"/>
-      <c r="E17" s="14"/>
+      <c r="E17" s="18"/>
     </row>
     <row r="18" spans="2:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="13"/>
+      <c r="B18" s="17"/>
       <c r="C18" s="22" t="s">
         <v>101</v>
       </c>
       <c r="D18" s="22"/>
-      <c r="E18" s="14"/>
+      <c r="E18" s="18"/>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="D19" s="13"/>
-      <c r="E19" s="14"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="18"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="14"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="18"/>
     </row>
     <row r="21" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B21" s="8"/>
@@ -2253,88 +2253,71 @@
       <c r="E21" s="8"/>
     </row>
     <row r="22" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
     </row>
     <row r="23" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
     </row>
     <row r="24" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
     </row>
     <row r="25" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B25" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
     </row>
     <row r="26" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B26" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B28" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="C11:C15"/>
-    <mergeCell ref="D11:D15"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E11:E15"/>
-    <mergeCell ref="B11:B15"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C5:D6"/>
-    <mergeCell ref="E4:E7"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="C28:E28"/>
     <mergeCell ref="B22:E22"/>
@@ -2349,6 +2332,23 @@
     <mergeCell ref="C25:E25"/>
     <mergeCell ref="C26:E26"/>
     <mergeCell ref="C27:E27"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C5:D6"/>
+    <mergeCell ref="E4:E7"/>
+    <mergeCell ref="C11:C15"/>
+    <mergeCell ref="D11:D15"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E11:E15"/>
+    <mergeCell ref="B11:B15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Docs/Characters.xlsx
+++ b/Docs/Characters.xlsx
@@ -459,7 +459,7 @@
     <t>Moving sandcastle, Suspicious dragon</t>
   </si>
   <si>
-    <t>Conductor, Battering boar, Sour snail, Living olive, Corn knight, dwarven eliminator, Siren</t>
+    <t>Conductor, Gas construct, Battering boar, Sour snail, Living olive, Corn knight, dwarven eliminator, Siren</t>
   </si>
 </sst>
 </file>
@@ -621,18 +621,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -646,6 +634,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -966,29 +966,29 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="17"/>
+      <c r="D4" s="13"/>
       <c r="E4" s="9" t="s">
         <v>2</v>
       </c>
@@ -997,90 +997,90 @@
       <c r="B5" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="D5" s="17"/>
+      <c r="D5" s="13"/>
       <c r="E5" s="10" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="D6" s="17"/>
-      <c r="E6" s="18" t="s">
+      <c r="D6" s="13"/>
+      <c r="E6" s="14" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B7" s="17"/>
-      <c r="C7" s="17" t="s">
+      <c r="B7" s="13"/>
+      <c r="C7" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="D7" s="17"/>
-      <c r="E7" s="18"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="14"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="18"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="14"/>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17" t="s">
+      <c r="D9" s="13"/>
+      <c r="E9" s="13" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="17"/>
-      <c r="C10" s="17" t="s">
+      <c r="B10" s="13"/>
+      <c r="C10" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="17"/>
-      <c r="C11" s="17" t="s">
+      <c r="B11" s="13"/>
+      <c r="C11" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="14" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B13" s="17"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="18"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="14"/>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B14" s="17"/>
+      <c r="B14" s="13"/>
       <c r="C14" s="9" t="s">
         <v>125</v>
       </c>
@@ -1092,54 +1092,54 @@
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B15" s="17"/>
-      <c r="C15" s="17" t="s">
+      <c r="B15" s="13"/>
+      <c r="C15" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="D15" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="E15" s="13" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
     </row>
     <row r="17" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="D17" s="17"/>
+      <c r="D17" s="13"/>
       <c r="E17" s="10" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="D18" s="17"/>
-      <c r="E18" s="18" t="s">
+      <c r="D18" s="13"/>
+      <c r="E18" s="14" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B19" s="17"/>
-      <c r="C19" s="17" t="s">
+      <c r="B19" s="13"/>
+      <c r="C19" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="D19" s="17"/>
-      <c r="E19" s="18"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="14"/>
     </row>
     <row r="20" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="8"/>
@@ -1148,55 +1148,70 @@
       <c r="E20" s="8"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B21" s="19" t="s">
+      <c r="B21" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="21"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="17"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="D22" s="13"/>
-      <c r="E22" s="14"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="19"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="D23" s="13"/>
-      <c r="E23" s="14"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="19"/>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="D24" s="13"/>
-      <c r="E24" s="14"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="19"/>
     </row>
     <row r="25" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="D25" s="15"/>
-      <c r="E25" s="16"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="B21:E21"/>
     <mergeCell ref="B12:B16"/>
     <mergeCell ref="C12:C13"/>
     <mergeCell ref="E12:E13"/>
@@ -1212,21 +1227,6 @@
     <mergeCell ref="E9:E11"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="C17:D17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1245,29 +1245,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
     </row>
     <row r="2" spans="2:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
     </row>
     <row r="3" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="17"/>
+      <c r="D3" s="13"/>
       <c r="E3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1276,94 +1276,94 @@
       <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="17"/>
+      <c r="D4" s="13"/>
       <c r="E4" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17" t="s">
+      <c r="D5" s="13"/>
+      <c r="E5" s="13" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6" s="17"/>
-      <c r="C6" s="17" t="s">
+      <c r="B6" s="13"/>
+      <c r="C6" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B7" s="17"/>
-      <c r="C7" s="17" t="s">
+      <c r="B7" s="13"/>
+      <c r="C7" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17" t="s">
+      <c r="D8" s="13"/>
+      <c r="E8" s="13" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="17"/>
-      <c r="C9" s="17" t="s">
+      <c r="B9" s="13"/>
+      <c r="C9" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="17"/>
-      <c r="C10" s="17" t="s">
+      <c r="B10" s="13"/>
+      <c r="C10" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
     </row>
     <row r="11" spans="2:5" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="14" t="s">
         <v>19</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B12" s="17"/>
-      <c r="C12" s="18"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="14"/>
       <c r="D12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="18"/>
+      <c r="E12" s="14"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B13" s="17"/>
+      <c r="B13" s="13"/>
       <c r="C13" s="1" t="s">
         <v>21</v>
       </c>
@@ -1375,7 +1375,7 @@
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B14" s="17"/>
+      <c r="B14" s="13"/>
       <c r="C14" s="1" t="s">
         <v>24</v>
       </c>
@@ -1387,7 +1387,7 @@
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B15" s="17"/>
+      <c r="B15" s="13"/>
       <c r="C15" s="1" t="s">
         <v>27</v>
       </c>
@@ -1402,33 +1402,33 @@
       <c r="B16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="17"/>
+      <c r="D16" s="13"/>
       <c r="E16" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17" t="s">
+      <c r="D17" s="13"/>
+      <c r="E17" s="13" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B18" s="17"/>
-      <c r="C18" s="17" t="s">
+      <c r="B18" s="13"/>
+      <c r="C18" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
     </row>
     <row r="19" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="8"/>
@@ -1437,63 +1437,60 @@
       <c r="E19" s="8"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="21"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="17"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D21" s="13"/>
-      <c r="E21" s="14"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="19"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="D22" s="13"/>
-      <c r="E22" s="14"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="19"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="D23" s="13"/>
-      <c r="E23" s="14"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="19"/>
     </row>
     <row r="24" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="D24" s="15"/>
-      <c r="E24" s="16"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="B11:B15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="E5:E7"/>
@@ -1508,11 +1505,14 @@
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="B11:B15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1532,29 +1532,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
     </row>
     <row r="2" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
     </row>
     <row r="3" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="17"/>
+      <c r="D3" s="13"/>
       <c r="E3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1563,141 +1563,141 @@
       <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="18"/>
+      <c r="D4" s="14"/>
       <c r="E4" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17" t="s">
+      <c r="D5" s="13"/>
+      <c r="E5" s="13" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="17"/>
-      <c r="C9" s="17" t="s">
+      <c r="B9" s="13"/>
+      <c r="C9" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="17"/>
-      <c r="C10" s="17" t="s">
+      <c r="B10" s="13"/>
+      <c r="C10" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="13" t="s">
         <v>17</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="E11" s="17"/>
+      <c r="E11" s="13"/>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B12" s="17"/>
+      <c r="B12" s="13"/>
       <c r="C12" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="E12" s="17"/>
+      <c r="E12" s="13"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B13" s="17"/>
+      <c r="B13" s="13"/>
       <c r="C13" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="17"/>
+      <c r="E13" s="13"/>
     </row>
     <row r="14" spans="2:5" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="17"/>
+      <c r="B14" s="13"/>
       <c r="C14" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="E14" s="18"/>
+      <c r="E14" s="14"/>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B15" s="17"/>
+      <c r="B15" s="13"/>
       <c r="C15" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="D15" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="17"/>
+      <c r="E15" s="13"/>
     </row>
     <row r="16" spans="2:5" ht="37.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
     </row>
     <row r="19" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B19" s="8"/>
@@ -1706,70 +1706,69 @@
       <c r="E19" s="8"/>
     </row>
     <row r="20" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
     </row>
     <row r="21" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B21" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
     </row>
     <row r="22" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B22" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
     </row>
     <row r="23" spans="2:5" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C23" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
     </row>
     <row r="24" spans="2:5" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="17"/>
-      <c r="C24" s="17" t="s">
+      <c r="B24" s="13"/>
+      <c r="C24" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
     </row>
     <row r="25" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B25" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="C5:D7"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C24:E24"/>
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="D12:E12"/>
@@ -1784,12 +1783,13 @@
     <mergeCell ref="C17:E18"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="C5:D7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1808,29 +1808,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
     </row>
     <row r="2" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
     </row>
     <row r="3" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="17"/>
+      <c r="D3" s="13"/>
       <c r="E3" s="4" t="s">
         <v>2</v>
       </c>
@@ -1839,137 +1839,137 @@
       <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18" t="s">
+      <c r="D4" s="14"/>
+      <c r="E4" s="14" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="17"/>
-      <c r="E5" s="18"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="14"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="18"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="14"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="18"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="14"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="18" t="s">
+      <c r="D8" s="13"/>
+      <c r="E8" s="14" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="17"/>
-      <c r="C9" s="17" t="s">
+      <c r="B9" s="13"/>
+      <c r="C9" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="17"/>
-      <c r="E9" s="18"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="14"/>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="17"/>
-      <c r="C10" s="17" t="s">
+      <c r="B10" s="13"/>
+      <c r="C10" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="17"/>
-      <c r="E10" s="18"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="14"/>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="14" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="12" spans="2:5" ht="67.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="17"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B13" s="17"/>
-      <c r="C13" s="17" t="s">
+      <c r="B13" s="13"/>
+      <c r="C13" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="13" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="17"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="13"/>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="17"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="13"/>
     </row>
     <row r="16" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="D16" s="18"/>
+      <c r="D16" s="14"/>
       <c r="E16" s="5" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17" t="s">
+      <c r="D17" s="13"/>
+      <c r="E17" s="13" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
     </row>
     <row r="19" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B19" s="8"/>
@@ -1978,62 +1978,60 @@
       <c r="E19" s="8"/>
     </row>
     <row r="20" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
     </row>
     <row r="21" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B21" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
     </row>
     <row r="22" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B22" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
     </row>
     <row r="23" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B23" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C23" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
     </row>
     <row r="24" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B24" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="C17:D18"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C24:E24"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="B11:B15"/>
     <mergeCell ref="C11:C12"/>
@@ -2050,11 +2048,13 @@
     <mergeCell ref="C5:D7"/>
     <mergeCell ref="D11:D12"/>
     <mergeCell ref="C13:C15"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="C17:D18"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="C16:D16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2073,29 +2073,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
     </row>
     <row r="2" spans="2:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
     </row>
     <row r="3" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="17"/>
+      <c r="D3" s="13"/>
       <c r="E3" s="7" t="s">
         <v>2</v>
       </c>
@@ -2104,147 +2104,147 @@
       <c r="B4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18" t="s">
+      <c r="D4" s="14"/>
+      <c r="E4" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="13" t="s">
         <v>90</v>
       </c>
       <c r="C5" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="D5" s="17"/>
-      <c r="E5" s="18"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="14"/>
     </row>
     <row r="6" spans="2:5" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="18"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="14"/>
     </row>
     <row r="7" spans="2:5" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="17"/>
+      <c r="B7" s="13"/>
       <c r="C7" s="22" t="s">
         <v>95</v>
       </c>
       <c r="D7" s="22"/>
-      <c r="E7" s="18"/>
+      <c r="E7" s="14"/>
     </row>
     <row r="8" spans="2:5" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="13" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>96</v>
       </c>
       <c r="D8" s="22"/>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="14" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="9" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="17"/>
+      <c r="B9" s="13"/>
       <c r="C9" s="22" t="s">
         <v>97</v>
       </c>
       <c r="D9" s="22"/>
-      <c r="E9" s="18"/>
+      <c r="E9" s="14"/>
     </row>
     <row r="10" spans="2:5" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="17"/>
+      <c r="B10" s="13"/>
       <c r="C10" s="22" t="s">
         <v>100</v>
       </c>
       <c r="D10" s="22"/>
-      <c r="E10" s="18"/>
+      <c r="E10" s="14"/>
     </row>
     <row r="11" spans="2:5" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="14" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B12" s="17"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B13" s="17"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B14" s="17"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B15" s="17"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
     </row>
     <row r="16" spans="2:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="13" t="s">
         <v>31</v>
       </c>
       <c r="C16" s="23" t="s">
         <v>98</v>
       </c>
       <c r="D16" s="23"/>
-      <c r="E16" s="18" t="s">
+      <c r="E16" s="14" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="17" spans="2:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="17"/>
+      <c r="B17" s="13"/>
       <c r="C17" s="22" t="s">
         <v>99</v>
       </c>
       <c r="D17" s="22"/>
-      <c r="E17" s="18"/>
+      <c r="E17" s="14"/>
     </row>
     <row r="18" spans="2:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="17"/>
+      <c r="B18" s="13"/>
       <c r="C18" s="22" t="s">
         <v>101</v>
       </c>
       <c r="D18" s="22"/>
-      <c r="E18" s="18"/>
+      <c r="E18" s="14"/>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="C19" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="D19" s="17"/>
-      <c r="E19" s="18"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="14"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="18"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="14"/>
     </row>
     <row r="21" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B21" s="8"/>
@@ -2253,71 +2253,88 @@
       <c r="E21" s="8"/>
     </row>
     <row r="22" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
     </row>
     <row r="23" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
     </row>
     <row r="24" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
     </row>
     <row r="25" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B25" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
     </row>
     <row r="26" spans="2:5" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B26" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C26" s="17" t="s">
+      <c r="C26" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C27" s="17" t="s">
+      <c r="C27" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B28" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="C11:C15"/>
+    <mergeCell ref="D11:D15"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E11:E15"/>
+    <mergeCell ref="B11:B15"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C5:D6"/>
+    <mergeCell ref="E4:E7"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="C28:E28"/>
     <mergeCell ref="B22:E22"/>
@@ -2332,23 +2349,6 @@
     <mergeCell ref="C25:E25"/>
     <mergeCell ref="C26:E26"/>
     <mergeCell ref="C27:E27"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C5:D6"/>
-    <mergeCell ref="E4:E7"/>
-    <mergeCell ref="C11:C15"/>
-    <mergeCell ref="D11:D15"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E11:E15"/>
-    <mergeCell ref="B11:B15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
